--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.76</v>
+        <v>337.55</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18.64</v>
+        <v>186.39</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17.67</v>
+        <v>176.67</v>
       </c>
     </row>
     <row r="5">
@@ -568,7 +568,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.01</v>
+        <v>170.06</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15.19</v>
+        <v>151.86</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.68</v>
+        <v>146.76</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.38</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +636,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.27</v>
+        <v>142.69</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.18</v>
+        <v>141.77</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.95</v>
+        <v>139.49</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11.92</v>
+        <v>119.19</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.21</v>
+        <v>112.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2021_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-05 07:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
